--- a/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N58_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T2372_W0066F0002T0006Z000C1N58_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.79163457716279</v>
+        <v>5.816140618788953</v>
       </c>
       <c r="D2" t="n">
-        <v>35.79083250093026</v>
+        <v>5.816010281401167</v>
       </c>
       <c r="E2" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F2" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.76340180124099</v>
+        <v>5.974052792701661</v>
       </c>
       <c r="D3" t="n">
-        <v>36.75790644881248</v>
+        <v>5.973159797932029</v>
       </c>
       <c r="E3" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F3" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.56639813250258</v>
+        <v>4.96703969653167</v>
       </c>
       <c r="D4" t="n">
-        <v>30.56719198460832</v>
+        <v>4.967168697498852</v>
       </c>
       <c r="E4" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F4" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>37.02297382733642</v>
+        <v>6.016233246942169</v>
       </c>
       <c r="D5" t="n">
-        <v>37.03090690722346</v>
+        <v>6.017522372423812</v>
       </c>
       <c r="E5" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F5" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>40.20986745439129</v>
+        <v>6.534103461338585</v>
       </c>
       <c r="D6" t="n">
-        <v>40.20028660042831</v>
+        <v>6.532546572569601</v>
       </c>
       <c r="E6" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F6" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.63813326825079</v>
+        <v>6.278696656090753</v>
       </c>
       <c r="D7" t="n">
-        <v>38.65050920697735</v>
+        <v>6.280707746133819</v>
       </c>
       <c r="E7" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F7" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.24268498993824</v>
+        <v>3.776936310864964</v>
       </c>
       <c r="D8" t="n">
-        <v>23.25716075421369</v>
+        <v>3.779288622559724</v>
       </c>
       <c r="E8" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F8" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.19628208798124</v>
+        <v>5.069395839296951</v>
       </c>
       <c r="D9" t="n">
-        <v>31.2103700160795</v>
+        <v>5.071685127612919</v>
       </c>
       <c r="E9" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F9" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>35.91712612958507</v>
+        <v>5.836532996057574</v>
       </c>
       <c r="D10" t="n">
-        <v>35.90277735157391</v>
+        <v>5.83420131963076</v>
       </c>
       <c r="E10" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F10" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>19.26514069167007</v>
+        <v>3.130585362396387</v>
       </c>
       <c r="D11" t="n">
-        <v>19.26158939720843</v>
+        <v>3.130008277046369</v>
       </c>
       <c r="E11" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F11" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.42136412310826</v>
+        <v>4.130971670005092</v>
       </c>
       <c r="D12" t="n">
-        <v>25.42642290769832</v>
+        <v>4.131793722500978</v>
       </c>
       <c r="E12" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F12" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>35.36188912068222</v>
+        <v>5.746306982110861</v>
       </c>
       <c r="D13" t="n">
-        <v>35.37250360713816</v>
+        <v>5.74803183615995</v>
       </c>
       <c r="E13" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F13" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>34.90513688516314</v>
+        <v>5.67208474383901</v>
       </c>
       <c r="D14" t="n">
-        <v>34.89423264552363</v>
+        <v>5.67031280489759</v>
       </c>
       <c r="E14" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F14" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>33.14765241427722</v>
+        <v>5.38649351732005</v>
       </c>
       <c r="D15" t="n">
-        <v>33.14680654895702</v>
+        <v>5.386356064205517</v>
       </c>
       <c r="E15" t="n">
-        <v>5.907834408479705</v>
+        <v>0.9600230913779521</v>
       </c>
       <c r="F15" t="n">
-        <v>5.905668563911664</v>
+        <v>0.9596711416356455</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
